--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -556,7 +556,7 @@
     <t>Bundle.entry</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>Entry in the bundle - will have a resource or information</t>
@@ -910,6 +910,9 @@
     <t>practitionerRole</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PractitionerRole {http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE}
 </t>
   </si>
@@ -921,9 +924,6 @@
   </si>
   <si>
     <t>organization</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">Organization {http://minsal.cl/listaespera/StructureDefinition/OrganizationLE}
@@ -17211,10 +17211,10 @@
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="F145" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>74</v>
@@ -17888,13 +17888,13 @@
         <v>74</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
@@ -20732,17 +20732,17 @@
         <v>170</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>74</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F177" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G177" t="s" s="2">
         <v>74</v>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
+++ b/refs/heads/master/StructureDefinition-BundleReferenciaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
